--- a/Koszty/Amortyzacja miesieczna Automaty.xlsx
+++ b/Koszty/Amortyzacja miesieczna Automaty.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studmsugedupl-my.sharepoint.com/personal/a_mazur_177_studms_ug_edu_pl/Documents/Dokumenty/Praca/P&amp;L/PiL_excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studmsugedupl-my.sharepoint.com/personal/a_mazur_177_studms_ug_edu_pl/Documents/Dokumenty/Praca/P&amp;L/PiL_excel/Koszty/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{5F1E0736-F1D5-4AD5-9E76-A1C611F77101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{809072BB-7EA2-4FF7-ADAD-F338B9016C0D}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{5F1E0736-F1D5-4AD5-9E76-A1C611F77101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C324EE1-FFEA-42D3-9114-D89382B8FCBF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" activeTab="1" xr2:uid="{F43583CD-4CA5-4225-8524-8CC9137B419C}"/>
+    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21600" xr2:uid="{F43583CD-4CA5-4225-8524-8CC9137B419C}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -622,9 +622,60 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -634,56 +685,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -693,12 +699,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1037,25 +1037,26 @@
   <dimension ref="A1:Q28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="24.140625" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="26.42578125" customWidth="1"/>
     <col min="6" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F1" s="56" t="s">
+      <c r="F1" s="58" t="s">
         <v>101</v>
       </c>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="58"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="60"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F2" s="3" t="s">
@@ -1105,10 +1106,10 @@
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="59" t="s">
+      <c r="D3" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="60"/>
+      <c r="E3" s="57"/>
       <c r="F3" s="6">
         <v>932.27</v>
       </c>
@@ -1136,10 +1137,10 @@
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="59" t="s">
+      <c r="D4" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="60"/>
+      <c r="E4" s="57"/>
       <c r="F4" s="6">
         <v>932.27</v>
       </c>
@@ -1167,10 +1168,10 @@
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="59" t="s">
+      <c r="D5" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="60"/>
+      <c r="E5" s="57"/>
       <c r="F5" s="6">
         <v>932.27</v>
       </c>
@@ -1198,10 +1199,10 @@
       <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="59" t="s">
+      <c r="D6" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="60"/>
+      <c r="E6" s="57"/>
       <c r="F6" s="6">
         <v>617.61</v>
       </c>
@@ -1229,10 +1230,10 @@
       <c r="C7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="59" t="s">
+      <c r="D7" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="60"/>
+      <c r="E7" s="57"/>
       <c r="F7" s="6">
         <v>1047.8900000000001</v>
       </c>
@@ -1260,10 +1261,10 @@
       <c r="C8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="59" t="s">
+      <c r="D8" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="60"/>
+      <c r="E8" s="57"/>
       <c r="F8" s="6">
         <v>1047.8900000000001</v>
       </c>
@@ -1291,10 +1292,10 @@
       <c r="C9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="59" t="s">
+      <c r="D9" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="60"/>
+      <c r="E9" s="57"/>
       <c r="F9" s="6">
         <v>1047.8900000000001</v>
       </c>
@@ -1322,10 +1323,10 @@
       <c r="C10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="59" t="s">
+      <c r="D10" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="60"/>
+      <c r="E10" s="57"/>
       <c r="F10" s="6">
         <v>1047.8900000000001</v>
       </c>
@@ -1353,10 +1354,10 @@
       <c r="C11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="59" t="s">
+      <c r="D11" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="60"/>
+      <c r="E11" s="57"/>
       <c r="F11" s="6">
         <v>1047.8900000000001</v>
       </c>
@@ -1384,10 +1385,10 @@
       <c r="C12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="59" t="s">
+      <c r="D12" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="60"/>
+      <c r="E12" s="57"/>
       <c r="F12" s="6">
         <v>1047.8900000000001</v>
       </c>
@@ -1415,10 +1416,10 @@
       <c r="C13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="59" t="s">
+      <c r="D13" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="60"/>
+      <c r="E13" s="57"/>
       <c r="F13" s="6">
         <v>1047.8900000000001</v>
       </c>
@@ -1446,10 +1447,10 @@
       <c r="C14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="59" t="s">
+      <c r="D14" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="60"/>
+      <c r="E14" s="57"/>
       <c r="F14" s="6">
         <v>1047.8900000000001</v>
       </c>
@@ -1477,10 +1478,10 @@
       <c r="C15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="59" t="s">
+      <c r="D15" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="60"/>
+      <c r="E15" s="57"/>
       <c r="F15" s="6">
         <v>1047.8900000000001</v>
       </c>
@@ -1539,10 +1540,10 @@
       <c r="C17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="59" t="s">
+      <c r="D17" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="60"/>
+      <c r="E17" s="57"/>
       <c r="F17" s="6">
         <v>2136.33</v>
       </c>
@@ -1570,10 +1571,10 @@
       <c r="C18" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="59" t="s">
+      <c r="D18" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="60"/>
+      <c r="E18" s="57"/>
       <c r="F18" s="6">
         <v>2143.25</v>
       </c>
@@ -1601,10 +1602,10 @@
       <c r="C19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="59" t="s">
+      <c r="D19" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="60"/>
+      <c r="E19" s="57"/>
       <c r="F19" s="6">
         <v>1096.25</v>
       </c>
@@ -1632,10 +1633,10 @@
       <c r="C20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="59" t="s">
+      <c r="D20" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="60"/>
+      <c r="E20" s="57"/>
       <c r="F20" s="6">
         <v>1096.25</v>
       </c>
@@ -1663,10 +1664,10 @@
       <c r="C21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="59" t="s">
+      <c r="D21" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="60"/>
+      <c r="E21" s="57"/>
       <c r="F21" s="6">
         <v>1096.25</v>
       </c>
@@ -1694,10 +1695,10 @@
       <c r="C22" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="59" t="s">
+      <c r="D22" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="E22" s="60"/>
+      <c r="E22" s="57"/>
       <c r="F22" s="6">
         <v>1041.74</v>
       </c>
@@ -1725,10 +1726,10 @@
       <c r="C23" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="59" t="s">
+      <c r="D23" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="E23" s="60"/>
+      <c r="E23" s="57"/>
       <c r="F23" s="6">
         <v>1041.74</v>
       </c>
@@ -1756,10 +1757,10 @@
       <c r="C24" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="59" t="s">
+      <c r="D24" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="E24" s="60"/>
+      <c r="E24" s="57"/>
       <c r="F24" s="6">
         <v>1041.74</v>
       </c>
@@ -1785,14 +1786,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
     <mergeCell ref="F1:Q1"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="D20:E20"/>
@@ -1807,6 +1800,14 @@
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1825,33 +1826,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="46" t="s">
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="42"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="8" t="s">
         <v>46</v>
       </c>
@@ -1861,10 +1862,10 @@
       <c r="D2" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="48" t="s">
+      <c r="E2" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="49"/>
+      <c r="F2" s="44"/>
       <c r="G2" s="8" t="s">
         <v>32</v>
       </c>
@@ -1906,13 +1907,13 @@
       <c r="A3" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="52"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="47"/>
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
       <c r="I3" s="13"/>
@@ -1927,12 +1928,12 @@
       <c r="R3" s="14"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="55"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="50"/>
       <c r="G4" s="15"/>
       <c r="H4" s="15"/>
       <c r="I4" s="15"/>
@@ -1962,7 +1963,7 @@
       <c r="E5" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="F5" s="39"/>
+      <c r="F5" s="35"/>
       <c r="G5" s="20">
         <v>862.79</v>
       </c>
@@ -1995,7 +1996,7 @@
       <c r="E6" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="39"/>
+      <c r="F6" s="35"/>
       <c r="G6" s="20">
         <v>862.79</v>
       </c>
@@ -2028,7 +2029,7 @@
       <c r="E7" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="39"/>
+      <c r="F7" s="35"/>
       <c r="G7" s="20">
         <v>862.79</v>
       </c>
@@ -2061,7 +2062,7 @@
       <c r="E8" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="39"/>
+      <c r="F8" s="35"/>
       <c r="G8" s="20">
         <v>862.79</v>
       </c>
@@ -2094,7 +2095,7 @@
       <c r="E9" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="39"/>
+      <c r="F9" s="35"/>
       <c r="G9" s="20">
         <v>862.79</v>
       </c>
@@ -2127,7 +2128,7 @@
       <c r="E10" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="39"/>
+      <c r="F10" s="35"/>
       <c r="G10" s="20">
         <v>862.79</v>
       </c>
@@ -2160,7 +2161,7 @@
       <c r="E11" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="39"/>
+      <c r="F11" s="35"/>
       <c r="G11" s="20">
         <v>862.79</v>
       </c>
@@ -2193,7 +2194,7 @@
       <c r="E12" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="39"/>
+      <c r="F12" s="35"/>
       <c r="G12" s="20">
         <v>862.79</v>
       </c>
@@ -2226,7 +2227,7 @@
       <c r="E13" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="39"/>
+      <c r="F13" s="35"/>
       <c r="G13" s="20">
         <v>862.79</v>
       </c>
@@ -2259,7 +2260,7 @@
       <c r="E14" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="F14" s="39"/>
+      <c r="F14" s="35"/>
       <c r="G14" s="20">
         <v>862.8</v>
       </c>
@@ -2292,7 +2293,7 @@
       <c r="E15" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="F15" s="39"/>
+      <c r="F15" s="35"/>
       <c r="G15" s="20">
         <v>767.95</v>
       </c>
@@ -2325,7 +2326,7 @@
       <c r="E16" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="39"/>
+      <c r="F16" s="35"/>
       <c r="G16" s="20">
         <v>789.5</v>
       </c>
@@ -2358,7 +2359,7 @@
       <c r="E17" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="F17" s="39"/>
+      <c r="F17" s="35"/>
       <c r="G17" s="20">
         <v>789.5</v>
       </c>
@@ -2391,7 +2392,7 @@
       <c r="E18" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="F18" s="39"/>
+      <c r="F18" s="35"/>
       <c r="G18" s="20">
         <v>789.5</v>
       </c>
@@ -2422,7 +2423,7 @@
       <c r="E19" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="39"/>
+      <c r="F19" s="35"/>
       <c r="G19" s="20">
         <v>789.5</v>
       </c>
@@ -2453,7 +2454,7 @@
       <c r="E20" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="F20" s="39"/>
+      <c r="F20" s="35"/>
       <c r="G20" s="20">
         <v>789.5</v>
       </c>
@@ -2484,7 +2485,7 @@
       <c r="E21" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="F21" s="39"/>
+      <c r="F21" s="35"/>
       <c r="G21" s="20">
         <v>789.5</v>
       </c>
@@ -2515,7 +2516,7 @@
       <c r="E22" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="F22" s="39"/>
+      <c r="F22" s="35"/>
       <c r="G22" s="20">
         <v>789.5</v>
       </c>
@@ -2546,7 +2547,7 @@
       <c r="E23" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="F23" s="39"/>
+      <c r="F23" s="35"/>
       <c r="G23" s="20">
         <v>789.5</v>
       </c>
@@ -2577,7 +2578,7 @@
       <c r="E24" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="F24" s="39"/>
+      <c r="F24" s="35"/>
       <c r="G24" s="20">
         <v>789.5</v>
       </c>
@@ -2608,7 +2609,7 @@
       <c r="E25" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="F25" s="39"/>
+      <c r="F25" s="35"/>
       <c r="G25" s="20">
         <v>789.5</v>
       </c>
@@ -2639,7 +2640,7 @@
       <c r="E26" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="F26" s="39"/>
+      <c r="F26" s="35"/>
       <c r="G26" s="22">
         <v>789.5</v>
       </c>
@@ -2670,7 +2671,7 @@
       <c r="E27" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="F27" s="39"/>
+      <c r="F27" s="35"/>
       <c r="G27" s="22">
         <v>810.61</v>
       </c>
@@ -2701,7 +2702,7 @@
       <c r="E28" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="F28" s="39"/>
+      <c r="F28" s="35"/>
       <c r="G28" s="22">
         <v>810.61</v>
       </c>
@@ -2732,7 +2733,7 @@
       <c r="E29" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="F29" s="39"/>
+      <c r="F29" s="35"/>
       <c r="G29" s="22">
         <v>801.73</v>
       </c>
@@ -2760,10 +2761,10 @@
       <c r="D30" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="E30" s="40" t="s">
+      <c r="E30" s="52" t="s">
         <v>84</v>
       </c>
-      <c r="F30" s="40"/>
+      <c r="F30" s="52"/>
       <c r="G30" s="26">
         <v>1606.85</v>
       </c>
@@ -2791,10 +2792,10 @@
       <c r="D31" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="E31" s="40" t="s">
+      <c r="E31" s="52" t="s">
         <v>85</v>
       </c>
-      <c r="F31" s="40"/>
+      <c r="F31" s="52"/>
       <c r="G31" s="22">
         <v>788.44</v>
       </c>
@@ -2825,7 +2826,7 @@
       <c r="E32" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="F32" s="35"/>
+      <c r="F32" s="51"/>
       <c r="G32" s="22">
         <v>788.44</v>
       </c>
@@ -2856,7 +2857,7 @@
       <c r="E33" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="F33" s="35"/>
+      <c r="F33" s="51"/>
       <c r="G33" s="22">
         <v>788.44</v>
       </c>
@@ -2887,7 +2888,7 @@
       <c r="E34" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="F34" s="35"/>
+      <c r="F34" s="51"/>
       <c r="G34" s="22">
         <v>788.44</v>
       </c>
@@ -2949,7 +2950,7 @@
       <c r="E36" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="F36" s="35"/>
+      <c r="F36" s="51"/>
       <c r="G36" s="22">
         <v>788.44</v>
       </c>
@@ -2980,7 +2981,7 @@
       <c r="E37" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="F37" s="35"/>
+      <c r="F37" s="51"/>
       <c r="G37" s="22">
         <v>788.44</v>
       </c>
@@ -3011,7 +3012,7 @@
       <c r="E38" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="F38" s="35"/>
+      <c r="F38" s="51"/>
       <c r="G38" s="22">
         <v>803.42</v>
       </c>
@@ -3042,7 +3043,7 @@
       <c r="E39" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="F39" s="35"/>
+      <c r="F39" s="51"/>
       <c r="G39" s="26">
         <v>788.44</v>
       </c>
@@ -3073,7 +3074,7 @@
       <c r="E40" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="F40" s="35"/>
+      <c r="F40" s="51"/>
       <c r="G40" s="26">
         <v>805.09</v>
       </c>
@@ -3104,7 +3105,7 @@
       <c r="E41" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="F41" s="35"/>
+      <c r="F41" s="51"/>
       <c r="G41" s="26">
         <v>805.09</v>
       </c>
@@ -3122,12 +3123,12 @@
       <c r="R41" s="26"/>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A42" s="36"/>
-      <c r="B42" s="37"/>
-      <c r="C42" s="37"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="38"/>
+      <c r="A42" s="53"/>
+      <c r="B42" s="54"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="55"/>
       <c r="G42" s="29">
         <f>SUM(G5:G41)</f>
         <v>30831.279999999988</v>
@@ -3176,16 +3177,27 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="G1:R1"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E31:F31"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="E10:F10"/>
@@ -3198,27 +3210,16 @@
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="G1:R1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
